--- a/Sample_Project/設計書/A1_プロジェクト管理システム/020_方式設計/020_開発標準/020_テスト標準/単体テスト仕様書(バッチ)_(取引ID)_(取引名).xlsx
+++ b/Sample_Project/設計書/A1_プロジェクト管理システム/020_方式設計/020_開発標準/020_テスト標準/単体テスト仕様書(バッチ)_(取引ID)_(取引名).xlsx
@@ -10929,8 +10929,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F11),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F11)&gt;0)*ROW($F$11:F11),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J11),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>1-1-1</v>
       </c>
@@ -10971,8 +10971,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F12),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F12)&gt;0)*ROW($F$11:F12),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J12),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>2-1-1</v>
       </c>
@@ -11007,8 +11007,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F13),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F13)&gt;0)*ROW($F$11:F13),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J13),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-1-1</v>
       </c>
@@ -11045,8 +11045,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F14),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F14)&gt;0)*ROW($F$11:F14),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J14),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-2-1</v>
       </c>
@@ -11079,8 +11079,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F15),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F15)&gt;0)*ROW($F$11:F15),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J15),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-3-1</v>
       </c>
@@ -11113,8 +11113,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F16),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F16)&gt;0)*ROW($F$11:F16),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J16),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-4-1</v>
       </c>
@@ -11147,8 +11147,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F17),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F17)&gt;0)*ROW($F$11:F17),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J17),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-5-1</v>
       </c>
@@ -11181,8 +11181,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F18),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F18)&gt;0)*ROW($F$11:F18),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J18),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-1-1</v>
       </c>
@@ -11219,8 +11219,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F19),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F19)&gt;0)*ROW($F$11:F19),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J19),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-2-1</v>
       </c>
@@ -11253,8 +11253,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F20),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F20)&gt;0)*ROW($F$11:F20),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J20),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-3-1</v>
       </c>
@@ -11287,8 +11287,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F21),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F21)&gt;0)*ROW($F$11:F21),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J21),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-1-1</v>
       </c>
@@ -11323,8 +11323,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F22),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F22)&gt;0)*ROW($F$11:F22),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J22),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-2-1</v>
       </c>
@@ -11357,8 +11357,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F23),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F23)&gt;0)*ROW($F$11:F23),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J23),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-3-1</v>
       </c>
@@ -11391,8 +11391,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F24),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F24)&gt;0)*ROW($F$11:F24),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J24),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-4-1</v>
       </c>
@@ -11425,8 +11425,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F25),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F25)&gt;0)*ROW($F$11:F25),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J25),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-1-1</v>
       </c>
@@ -11463,8 +11463,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F26),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F26)&gt;0)*ROW($F$11:F26),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J26),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-2-1</v>
       </c>
@@ -11497,8 +11497,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F27),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F27)&gt;0)*ROW($F$11:F27),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J27),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-1-1</v>
       </c>
@@ -11535,8 +11535,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F28),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F28)&gt;0)*ROW($F$11:F28),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J28),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-2-1</v>
       </c>
@@ -11569,8 +11569,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F29),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F29)&gt;0)*ROW($F$11:F29),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J29),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-1-1</v>
       </c>
@@ -11605,8 +11605,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F30),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F30)&gt;0)*ROW($F$11:F30),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J30),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-2-1</v>
       </c>
@@ -11639,8 +11639,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F31),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F31)&gt;0)*ROW($F$11:F31),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J31),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-3-1</v>
       </c>
@@ -11673,8 +11673,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F32),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F32)&gt;0)*ROW($F$11:F32),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J32),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-4-1</v>
       </c>
@@ -11707,8 +11707,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F33),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F33)&gt;0)*ROW($F$11:F33),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J33),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-1-1</v>
       </c>
@@ -11743,8 +11743,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F34),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F34)&gt;0)*ROW($F$11:F34),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J34),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-2-1</v>
       </c>
@@ -11777,8 +11777,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F35),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F35)&gt;0)*ROW($F$11:F35),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J35),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>10-1-1</v>
       </c>
@@ -11813,8 +11813,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F36),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F36)&gt;0)*ROW($F$11:F36),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J36),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-1-1</v>
       </c>
@@ -11851,8 +11851,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F37),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F37)&gt;0)*ROW($F$11:F37),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J37),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-2-1</v>
       </c>
@@ -11883,8 +11883,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F38),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F38)&gt;0)*ROW($F$11:F38),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J38),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-3-1</v>
       </c>
@@ -11915,8 +11915,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F39),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F39)&gt;0)*ROW($F$11:F39),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J39),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-4-1</v>
       </c>
@@ -11947,8 +11947,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F40),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F40)&gt;0)*ROW($F$11:F40),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J40),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-1-1</v>
       </c>
@@ -11985,8 +11985,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F41),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F41)&gt;0)*ROW($F$11:F41),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J41),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-2-1</v>
       </c>
@@ -12019,8 +12019,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F42),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F42)&gt;0)*ROW($F$11:F42),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J42),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-1-1</v>
       </c>
@@ -12061,8 +12061,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F43),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F43)&gt;0)*ROW($F$11:F43),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J43),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-2-1</v>
       </c>
@@ -12095,8 +12095,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F44),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F44)&gt;0)*ROW($F$11:F44),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J44),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-3-1</v>
       </c>
@@ -12129,8 +12129,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F45),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F45)&gt;0)*ROW($F$11:F45),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J45),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-1-1</v>
       </c>
@@ -12165,8 +12165,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F46),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F46)&gt;0)*ROW($F$11:F46),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J46),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-2-1</v>
       </c>
@@ -12199,8 +12199,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F47),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F47)&gt;0)*ROW($F$11:F47),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J47),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-3-1</v>
       </c>
@@ -12233,8 +12233,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F48),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F48)&gt;0)*ROW($F$11:F48),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J48),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-1-1</v>
       </c>
@@ -12269,8 +12269,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F49),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F49)&gt;0)*ROW($F$11:F49),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J49),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-2-1</v>
       </c>
@@ -12303,8 +12303,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F50),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F50)&gt;0)*ROW($F$11:F50),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J50),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-1-1</v>
       </c>
@@ -12339,8 +12339,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F51),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F51)&gt;0)*ROW($F$11:F51),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J51),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-2-1</v>
       </c>
@@ -12373,8 +12373,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F52),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F52)&gt;0)*ROW($F$11:F52),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J52),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-3-1</v>
       </c>
@@ -12407,8 +12407,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F53),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F53)&gt;0)*ROW($F$11:F53),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J53),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-4-1</v>
       </c>
@@ -12441,8 +12441,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F54),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F54)&gt;0)*ROW($F$11:F54),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J54),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-5-1</v>
       </c>
@@ -12475,8 +12475,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F55),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F55)&gt;0)*ROW($F$11:F55),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J55),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-6-1</v>
       </c>
@@ -12509,8 +12509,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F56),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F56)&gt;0)*ROW($F$11:F56),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J56),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>17-1-1</v>
       </c>
@@ -12545,8 +12545,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F57),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F57)&gt;0)*ROW($F$11:F57),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J57),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>18-1-1</v>
       </c>
@@ -12581,8 +12581,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F58),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F58)&gt;0)*ROW($F$11:F58),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J58),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>19-1-1</v>
       </c>
@@ -12617,8 +12617,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F59),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F59)&gt;0)*ROW($F$11:F59),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J59),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-1-1</v>
       </c>
@@ -12655,8 +12655,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F60),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F60)&gt;0)*ROW($F$11:F60),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J60),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-2-1</v>
       </c>
@@ -12689,8 +12689,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F61),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F61)&gt;0)*ROW($F$11:F61),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J61),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-3-1</v>
       </c>
@@ -12723,8 +12723,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F62),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F62)&gt;0)*ROW($F$11:F62),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J62),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-4-1</v>
       </c>
@@ -12757,8 +12757,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F63),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F63)&gt;0)*ROW($F$11:F63),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J63),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-5-1</v>
       </c>
@@ -12791,8 +12791,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F64),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F64)&gt;0)*ROW($F$11:F64),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J64),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-1-1</v>
       </c>
@@ -12827,8 +12827,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F65),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F65)&gt;0)*ROW($F$11:F65),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J65),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-2-1</v>
       </c>
@@ -12861,8 +12861,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F66),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F66)&gt;0)*ROW($F$11:F66),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J66),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-3-1</v>
       </c>
@@ -12895,8 +12895,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F67),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F67)&gt;0)*ROW($F$11:F67),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J67),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-4-1</v>
       </c>
@@ -12929,8 +12929,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F68),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F68)&gt;0)*ROW($F$11:F68),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J68),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-5-1</v>
       </c>
@@ -12963,8 +12963,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F69),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F69)&gt;0)*ROW($F$11:F69),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J69),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-6-1</v>
       </c>
@@ -12997,8 +12997,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F70),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F70)&gt;0)*ROW($F$11:F70),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J70),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-7-1</v>
       </c>
@@ -13031,8 +13031,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F71),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F71)&gt;0)*ROW($F$11:F71),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J71),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-8-1</v>
       </c>
@@ -13065,8 +13065,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F72),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F72)&gt;0)*ROW($F$11:F72),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J72),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-1-1</v>
       </c>
@@ -13101,8 +13101,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F73),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F73)&gt;0)*ROW($F$11:F73),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J73),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-1-1</v>
       </c>
@@ -13137,8 +13137,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F74),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F74)&gt;0)*ROW($F$11:F74),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J74),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-2-1</v>
       </c>
@@ -13171,8 +13171,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F75),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F75)&gt;0)*ROW($F$11:F75),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J75),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-3-1</v>
       </c>
@@ -13205,8 +13205,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F76),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F76)&gt;0)*ROW($F$11:F76),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J76),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-4-1</v>
       </c>
@@ -13239,8 +13239,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F77),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F77)&gt;0)*ROW($F$11:F77),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J77),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-5-1</v>
       </c>
@@ -13273,8 +13273,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F78),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F78)&gt;0)*ROW($F$11:F78),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J78),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-1-1</v>
       </c>
@@ -13313,8 +13313,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F79),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F79)&gt;0)*ROW($F$11:F79),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J79),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-2-1</v>
       </c>
@@ -13347,8 +13347,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F80),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F80)&gt;0)*ROW($F$11:F80),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J80),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>25-1-1</v>
       </c>
@@ -13383,8 +13383,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F81),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F81)&gt;0)*ROW($F$11:F81),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J81),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-1-1</v>
       </c>
@@ -13419,8 +13419,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F82),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F82)&gt;0)*ROW($F$11:F82),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J82),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-2-1</v>
       </c>
@@ -13453,8 +13453,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F83),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F83)&gt;0)*ROW($F$11:F83),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J83),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>27-1-1</v>
       </c>
@@ -13489,8 +13489,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F84),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F84)&gt;0)*ROW($F$11:F84),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J84),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>28-1-1</v>
       </c>
@@ -13525,8 +13525,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F85),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F85)&gt;0)*ROW($F$11:F85),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J85),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>29-1-1</v>
       </c>
@@ -13565,8 +13565,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F86),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F86)&gt;0)*ROW($F$11:F86),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J86),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>30-1-1</v>
       </c>
@@ -13601,8 +13601,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F87),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F87)&gt;0)*ROW($F$11:F87),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J87),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>31-1-1</v>
       </c>
@@ -13637,8 +13637,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F88),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F88)&gt;0)*ROW($F$11:F88),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J88),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-1-1</v>
       </c>
@@ -13677,8 +13677,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F89),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F89)&gt;0)*ROW($F$11:F89),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J89),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-2-1</v>
       </c>
@@ -13711,8 +13711,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F90),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F90)&gt;0)*ROW($F$11:F90),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J90),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>33-1-1</v>
       </c>
@@ -13747,8 +13747,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F91),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F91)&gt;0)*ROW($F$11:F91),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J91),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-1-1</v>
       </c>
@@ -13783,8 +13783,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F92),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F92)&gt;0)*ROW($F$11:F92),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J92),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-2-1</v>
       </c>
@@ -13817,8 +13817,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F93),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F93)&gt;0)*ROW($F$11:F93),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J93),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>35-1-1</v>
       </c>
@@ -13853,8 +13853,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F94),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F94)&gt;0)*ROW($F$11:F94),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J94),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-1-1</v>
       </c>
@@ -13893,8 +13893,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F95),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F95)&gt;0)*ROW($F$11:F95),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J95),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-2-1</v>
       </c>
@@ -13927,8 +13927,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F96),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F96)&gt;0)*ROW($F$11:F96),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J96),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-3-1</v>
       </c>
@@ -13961,8 +13961,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F97),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F97)&gt;0)*ROW($F$11:F97),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J97),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-4-1</v>
       </c>
@@ -13995,8 +13995,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F98),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F98)&gt;0)*ROW($F$11:F98),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J98),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-5-1</v>
       </c>
@@ -14029,8 +14029,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F99),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F99)&gt;0)*ROW($F$11:F99),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J99),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-1-1</v>
       </c>
@@ -14065,8 +14065,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F100),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F100)&gt;0)*ROW($F$11:F100),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J100),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-2-1</v>
       </c>
@@ -14099,8 +14099,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F101),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F101)&gt;0)*ROW($F$11:F101),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J101),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-3-1</v>
       </c>
@@ -14133,8 +14133,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F102),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F102)&gt;0)*ROW($F$11:F102),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J102),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-4-1</v>
       </c>
@@ -14167,8 +14167,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F103),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F103)&gt;0)*ROW($F$11:F103),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J103),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-5-1</v>
       </c>
@@ -14201,8 +14201,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F104),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F104)&gt;0)*ROW($F$11:F104),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J104),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>38-1-1</v>
       </c>
@@ -14237,8 +14237,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F105),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F105)&gt;0)*ROW($F$11:F105),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J105),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>39-1-1</v>
       </c>
@@ -14279,8 +14279,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F106),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F106)&gt;0)*ROW($F$11:F106),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J106),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-1-1</v>
       </c>
@@ -14319,8 +14319,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F107),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F107)&gt;0)*ROW($F$11:F107),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J107),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-2-1</v>
       </c>
@@ -14353,8 +14353,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F108),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F108)&gt;0)*ROW($F$11:F108),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J108),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>41-1-1</v>
       </c>
@@ -14393,8 +14393,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F109),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F109)&gt;0)*ROW($F$11:F109),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J109),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-1-1</v>
       </c>
@@ -14433,8 +14433,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F110),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F110)&gt;0)*ROW($F$11:F110),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J110),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-2-1</v>
       </c>
@@ -14467,8 +14467,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F111),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F111)&gt;0)*ROW($F$11:F111),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J111),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-1-1</v>
       </c>
@@ -14509,8 +14509,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F112),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F112)&gt;0)*ROW($F$11:F112),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J112),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-2-1</v>
       </c>
@@ -14545,8 +14545,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F113),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F113)&gt;0)*ROW($F$11:F113),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J113),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-3-1</v>
       </c>
@@ -14579,8 +14579,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F114),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F114)&gt;0)*ROW($F$11:F114),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J114),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-4-1</v>
       </c>
@@ -14613,8 +14613,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F115),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F115)&gt;0)*ROW($F$11:F115),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J115),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-1-1</v>
       </c>
@@ -14649,8 +14649,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F116),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F116)&gt;0)*ROW($F$11:F116),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J116),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-2-1</v>
       </c>
@@ -14683,8 +14683,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F117),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F117)&gt;0)*ROW($F$11:F117),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J117),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-3-1</v>
       </c>
@@ -14717,8 +14717,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F118),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F118)&gt;0)*ROW($F$11:F118),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J118),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-4-1</v>
       </c>
@@ -14751,8 +14751,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F119),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F119)&gt;0)*ROW($F$11:F119),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J119),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-5-1</v>
       </c>
@@ -14785,8 +14785,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F120),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F120)&gt;0)*ROW($F$11:F120),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J120),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-1-1</v>
       </c>
@@ -14821,8 +14821,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F121),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F121)&gt;0)*ROW($F$11:F121),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J121),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-2-1</v>
       </c>
@@ -14855,8 +14855,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F122),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F122)&gt;0)*ROW($F$11:F122),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J122),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-3-1</v>
       </c>
@@ -14889,8 +14889,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F123),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F123)&gt;0)*ROW($F$11:F123),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J123),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-4-1</v>
       </c>
@@ -14923,8 +14923,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F124),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F124)&gt;0)*ROW($F$11:F124),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J124),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-5-1</v>
       </c>
@@ -14957,8 +14957,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F125),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F125)&gt;0)*ROW($F$11:F125),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J125),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>46-1-1</v>
       </c>
@@ -14993,8 +14993,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F126),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F126)&gt;0)*ROW($F$11:F126),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J126),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>47-1-1</v>
       </c>
@@ -15031,8 +15031,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F127),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F127)&gt;0)*ROW($F$11:F127),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J127),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>48-1-1</v>
       </c>
@@ -15071,8 +15071,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F128),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F128)&gt;0)*ROW($F$11:F128),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J128),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-1-1</v>
       </c>
@@ -15107,8 +15107,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F129),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F129)&gt;0)*ROW($F$11:F129),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J129),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-2-1</v>
       </c>
@@ -15141,8 +15141,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F130),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F130)&gt;0)*ROW($F$11:F130),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J130),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-3-1</v>
       </c>
@@ -15175,8 +15175,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F131),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F131)&gt;0)*ROW($F$11:F131),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J131),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-1-1</v>
       </c>
@@ -15217,8 +15217,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F132),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F132)&gt;0)*ROW($F$11:F132),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J132),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-2-1</v>
       </c>
@@ -15253,8 +15253,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F133),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F133)&gt;0)*ROW($F$11:F133),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J133),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-3-1</v>
       </c>
@@ -15287,8 +15287,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F134),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F134)&gt;0)*ROW($F$11:F134),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J134),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-4-1</v>
       </c>
@@ -15321,8 +15321,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F135),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F135)&gt;0)*ROW($F$11:F135),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J135),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-1-1</v>
       </c>
@@ -15357,8 +15357,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F136),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F136)&gt;0)*ROW($F$11:F136),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J136),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-2-1</v>
       </c>
@@ -15391,8 +15391,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F137),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F137)&gt;0)*ROW($F$11:F137),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J137),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>52-1-1</v>
       </c>
@@ -15429,8 +15429,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F138),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F138)&gt;0)*ROW($F$11:F138),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J138),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>53-1-1</v>
       </c>
@@ -15469,8 +15469,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F139),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F139)&gt;0)*ROW($F$11:F139),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J139),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>54-1-1</v>
       </c>
@@ -15505,8 +15505,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F140),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F140)&gt;0)*ROW($F$11:F140),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J140),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>55-1-1</v>
       </c>
@@ -15541,8 +15541,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F141),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F141)&gt;0)*ROW($F$11:F141),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J141),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>56-1-1</v>
       </c>
@@ -15577,8 +15577,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F142),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F142)&gt;0)*ROW($F$11:F142),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J142),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>57-1-1</v>
       </c>
@@ -15613,8 +15613,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F143),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F143)&gt;0)*ROW($F$11:F143),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J143),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-1-1</v>
       </c>
@@ -15649,8 +15649,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F144),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F144)&gt;0)*ROW($F$11:F144),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J144),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-2-1</v>
       </c>
@@ -15683,8 +15683,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F145),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F145)&gt;0)*ROW($F$11:F145),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J145),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-3-1</v>
       </c>
@@ -15717,8 +15717,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F146),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F146)&gt;0)*ROW($F$11:F146),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J146),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-4-1</v>
       </c>
@@ -15751,8 +15751,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F147),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F147)&gt;0)*ROW($F$11:F147),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J147),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-5-1</v>
       </c>
@@ -15785,8 +15785,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F148),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F148)&gt;0)*ROW($F$11:F148),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J148),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-6-1</v>
       </c>
@@ -15819,8 +15819,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F149),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F149)&gt;0)*ROW($F$11:F149),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J149),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-1-1</v>
       </c>
@@ -15857,8 +15857,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F150),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F150)&gt;0)*ROW($F$11:F150),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J150),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-2-1</v>
       </c>
@@ -15891,8 +15891,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F151),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F151)&gt;0)*ROW($F$11:F151),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J151),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-1-1</v>
       </c>
@@ -15927,8 +15927,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F152),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F152)&gt;0)*ROW($F$11:F152),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J152),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-2-1</v>
       </c>
@@ -15961,8 +15961,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F153),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F153)&gt;0)*ROW($F$11:F153),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J153),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-3-1</v>
       </c>
@@ -15995,8 +15995,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F154),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F154)&gt;0)*ROW($F$11:F154),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J154),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-4-1</v>
       </c>
@@ -16029,8 +16029,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F155),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F155)&gt;0)*ROW($F$11:F155),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J155),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-5-1</v>
       </c>
@@ -16063,8 +16063,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F156),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F156)&gt;0)*ROW($F$11:F156),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J156),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-6-1</v>
       </c>
@@ -16097,8 +16097,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F157),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F157)&gt;0)*ROW($F$11:F157),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J157),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-7-1</v>
       </c>
@@ -16131,8 +16131,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F158),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F158)&gt;0)*ROW($F$11:F158),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J158),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-8-1</v>
       </c>
@@ -16165,8 +16165,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F159),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F159)&gt;0)*ROW($F$11:F159),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J159),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-9-1</v>
       </c>
@@ -16199,8 +16199,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F160),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F160)&gt;0)*ROW($F$11:F160),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J160),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-10-1</v>
       </c>
@@ -16233,8 +16233,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F161),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F161)&gt;0)*ROW($F$11:F161),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J161),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-11-1</v>
       </c>
@@ -16267,8 +16267,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F162),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F162)&gt;0)*ROW($F$11:F162),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J162),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-1-1</v>
       </c>
@@ -16303,8 +16303,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F163),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F163)&gt;0)*ROW($F$11:F163),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J163),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-2-1</v>
       </c>
@@ -16337,8 +16337,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F164),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F164)&gt;0)*ROW($F$11:F164),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J164),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-3-1</v>
       </c>
@@ -16371,8 +16371,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F165),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F165)&gt;0)*ROW($F$11:F165),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J165),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-4-1</v>
       </c>
@@ -16405,8 +16405,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F166),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F166)&gt;0)*ROW($F$11:F166),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J166),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-5-1</v>
       </c>
@@ -16439,8 +16439,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F167),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F167)&gt;0)*ROW($F$11:F167),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J167),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-6-1</v>
       </c>
@@ -16473,8 +16473,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F168),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F168)&gt;0)*ROW($F$11:F168),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J168),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-7-1</v>
       </c>
@@ -16507,8 +16507,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F169),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F169)&gt;0)*ROW($F$11:F169),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J169),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-1-1</v>
       </c>
@@ -16543,8 +16543,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F170),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F170)&gt;0)*ROW($F$11:F170),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J170),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-2-1</v>
       </c>
@@ -16577,8 +16577,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F171),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F171)&gt;0)*ROW($F$11:F171),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J171),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-3-1</v>
       </c>
@@ -16611,8 +16611,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F172),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F172)&gt;0)*ROW($F$11:F172),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J172),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-4-1</v>
       </c>
@@ -16645,8 +16645,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F173),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F173)&gt;0)*ROW($F$11:F173),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J173),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-5-1</v>
       </c>
@@ -16679,8 +16679,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F174),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F174)&gt;0)*ROW($F$11:F174),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J174),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-6-1</v>
       </c>
@@ -16713,8 +16713,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F175),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F175)&gt;0)*ROW($F$11:F175),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J175),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-7-1</v>
       </c>
@@ -16747,8 +16747,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F176),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F176)&gt;0)*ROW($F$11:F176),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J176),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-8-1</v>
       </c>
@@ -16781,8 +16781,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F177),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F177)&gt;0)*ROW($F$11:F177),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J177),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-9-1</v>
       </c>
@@ -16815,8 +16815,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F178),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F178)&gt;0)*ROW($F$11:F178),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J178),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-1-1</v>
       </c>
@@ -16851,8 +16851,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F179),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F179)&gt;0)*ROW($F$11:F179),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J179),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-1-1</v>
       </c>
@@ -16887,8 +16887,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F180),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F180)&gt;0)*ROW($F$11:F180),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J180),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>65-1-1</v>
       </c>
@@ -16929,8 +16929,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F181),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F181)&gt;0)*ROW($F$11:F181),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J181),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>66-1-1</v>
       </c>
@@ -16967,8 +16967,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F182),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F182)&gt;0)*ROW($F$11:F182),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J182),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>67-1-1</v>
       </c>
@@ -17005,8 +17005,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F183),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F183)&gt;0)*ROW($F$11:F183),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J183),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>68-1-1</v>
       </c>
@@ -17047,8 +17047,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F184),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F184)&gt;0)*ROW($F$11:F184),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J184),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-1-1</v>
       </c>
@@ -17083,8 +17083,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F185),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F185)&gt;0)*ROW($F$11:F185),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J185),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-2-1</v>
       </c>
@@ -17117,8 +17117,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F186),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F186)&gt;0)*ROW($F$11:F186),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J186),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-1-1</v>
       </c>
@@ -17153,8 +17153,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F187),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F187)&gt;0)*ROW($F$11:F187),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J187),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-2-1</v>
       </c>
@@ -17187,8 +17187,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F188),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F188)&gt;0)*ROW($F$11:F188),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J188),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>71-1-1</v>
       </c>
@@ -17225,8 +17225,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F189),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F189)&gt;0)*ROW($F$11:F189),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J189),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-1-1</v>
       </c>
@@ -17265,8 +17265,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F190),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F190)&gt;0)*ROW($F$11:F190),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J190),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-2-1</v>
       </c>
@@ -17299,8 +17299,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F191),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F191)&gt;0)*ROW($F$11:F191),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J191),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-3-1</v>
       </c>
@@ -17333,8 +17333,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F192),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F192)&gt;0)*ROW($F$11:F192),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J192),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-4-1</v>
       </c>
@@ -17367,8 +17367,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F193),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F193)&gt;0)*ROW($F$11:F193),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J193),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-5-1</v>
       </c>
@@ -17401,8 +17401,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F194),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F194)&gt;0)*ROW($F$11:F194),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J194),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-6-1</v>
       </c>
@@ -17435,8 +17435,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F195),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F195)&gt;0)*ROW($F$11:F195),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J195),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-7-1</v>
       </c>
@@ -17469,8 +17469,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F196),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F196)&gt;0)*ROW($F$11:F196),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J196),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>73-1-1</v>
       </c>
@@ -17505,8 +17505,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F197),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F197)&gt;0)*ROW($F$11:F197),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J197),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-1-1</v>
       </c>
@@ -17543,8 +17543,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F198),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F198)&gt;0)*ROW($F$11:F198),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J198),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-2-1</v>
       </c>
@@ -17577,8 +17577,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F199),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F199)&gt;0)*ROW($F$11:F199),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J199),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-3-1</v>
       </c>
@@ -17611,8 +17611,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F200),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F200)&gt;0)*ROW($F$11:F200),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J200),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-4-1</v>
       </c>
@@ -17645,8 +17645,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F201),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F201)&gt;0)*ROW($F$11:F201),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J201),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-5-1</v>
       </c>
@@ -17679,8 +17679,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F202),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F202)&gt;0)*ROW($F$11:F202),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J202),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-6-1</v>
       </c>
@@ -17713,8 +17713,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F203),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F203)&gt;0)*ROW($F$11:F203),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J203),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-7-1</v>
       </c>
@@ -17747,8 +17747,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F204),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F204)&gt;0)*ROW($F$11:F204),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J204),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-8-1</v>
       </c>
@@ -17781,8 +17781,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F205),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F205)&gt;0)*ROW($F$11:F205),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J205),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-9-1</v>
       </c>
@@ -17815,8 +17815,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F206),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F206)&gt;0)*ROW($F$11:F206),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J206),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-10-1</v>
       </c>
@@ -17849,8 +17849,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F207),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F207)&gt;0)*ROW($F$11:F207),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J207),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-11-1</v>
       </c>
@@ -17883,8 +17883,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F208),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F208)&gt;0)*ROW($F$11:F208),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J208),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-12-1</v>
       </c>
@@ -17917,8 +17917,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F209),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F209)&gt;0)*ROW($F$11:F209),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J209),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-13-1</v>
       </c>
@@ -17951,8 +17951,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F210),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F210)&gt;0)*ROW($F$11:F210),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J210),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-1-1</v>
       </c>
@@ -17989,8 +17989,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F211),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F211)&gt;0)*ROW($F$11:F211),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J211),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-2-1</v>
       </c>
@@ -18023,8 +18023,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F212),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F212)&gt;0)*ROW($F$11:F212),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J212),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-3-1</v>
       </c>
@@ -18057,8 +18057,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F213),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F213)&gt;0)*ROW($F$11:F213),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J213),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-4-1</v>
       </c>
@@ -18091,8 +18091,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F214),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F214)&gt;0)*ROW($F$11:F214),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J214),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-5-1</v>
       </c>
@@ -18125,8 +18125,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F215),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F215)&gt;0)*ROW($F$11:F215),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J215),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-6-1</v>
       </c>
@@ -18159,8 +18159,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F216),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F216)&gt;0)*ROW($F$11:F216),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J216),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-7-1</v>
       </c>
@@ -18193,8 +18193,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F217),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F217)&gt;0)*ROW($F$11:F217),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J217),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-8-1</v>
       </c>
@@ -18227,8 +18227,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F218),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F218)&gt;0)*ROW($F$11:F218),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J218),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-9-1</v>
       </c>
@@ -18261,8 +18261,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F219),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F219)&gt;0)*ROW($F$11:F219),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J219),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-10-1</v>
       </c>
@@ -18295,8 +18295,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F220),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F220)&gt;0)*ROW($F$11:F220),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J220),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-11-1</v>
       </c>
@@ -18329,8 +18329,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F221),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F221)&gt;0)*ROW($F$11:F221),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J221),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-12-1</v>
       </c>
@@ -18363,8 +18363,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F222),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F222)&gt;0)*ROW($F$11:F222),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J222),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-13-1</v>
       </c>
@@ -18397,8 +18397,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F223),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F223)&gt;0)*ROW($F$11:F223),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J223),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-14-1</v>
       </c>
@@ -18431,8 +18431,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F224),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F224)&gt;0)*ROW($F$11:F224),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J224),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-15-1</v>
       </c>
@@ -18465,8 +18465,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F225),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F225)&gt;0)*ROW($F$11:F225),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J225),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-1-1</v>
       </c>
@@ -18501,8 +18501,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F226),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F226)&gt;0)*ROW($F$11:F226),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J226),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-2-1</v>
       </c>
@@ -18535,8 +18535,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F227),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F227)&gt;0)*ROW($F$11:F227),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J227),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-3-1</v>
       </c>
@@ -18569,8 +18569,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F228),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F228)&gt;0)*ROW($F$11:F228),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J228),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-1-1</v>
       </c>
@@ -18605,8 +18605,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F229),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F229)&gt;0)*ROW($F$11:F229),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J229),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>78-1-1</v>
       </c>
@@ -18641,8 +18641,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F230),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F230)&gt;0)*ROW($F$11:F230),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J230),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>79-1-1</v>
       </c>
@@ -18683,8 +18683,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F231),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F231)&gt;0)*ROW($F$11:F231),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J231),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-1-1</v>
       </c>
@@ -18719,8 +18719,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F232),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F232)&gt;0)*ROW($F$11:F232),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J232),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-2-1</v>
       </c>
@@ -18753,8 +18753,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F233),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F233)&gt;0)*ROW($F$11:F233),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J233),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-3-1</v>
       </c>
@@ -18787,8 +18787,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F234),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F234)&gt;0)*ROW($F$11:F234),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J234),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-4-1</v>
       </c>
@@ -18821,8 +18821,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F235),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F235)&gt;0)*ROW($F$11:F235),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J235),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-5-1</v>
       </c>
@@ -18855,8 +18855,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F236),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F236)&gt;0)*ROW($F$11:F236),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J236),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-1-1</v>
       </c>
@@ -18891,8 +18891,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F237),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F237)&gt;0)*ROW($F$11:F237),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J237),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-2-1</v>
       </c>
@@ -18925,8 +18925,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F238),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F238)&gt;0)*ROW($F$11:F238),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J238),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-3-1</v>
       </c>
@@ -18959,8 +18959,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F239),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F239)&gt;0)*ROW($F$11:F239),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J239),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-4-1</v>
       </c>
@@ -18993,8 +18993,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F240),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F240)&gt;0)*ROW($F$11:F240),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J240),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-5-1</v>
       </c>
@@ -19027,8 +19027,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F241),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F241)&gt;0)*ROW($F$11:F241),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J241),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>82-1-1</v>
       </c>
@@ -19063,8 +19063,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F242),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F242)&gt;0)*ROW($F$11:F242),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J242),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>83-1-1</v>
       </c>
@@ -19103,8 +19103,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F243),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F243)&gt;0)*ROW($F$11:F243),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J243),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-1-1</v>
       </c>
@@ -19145,8 +19145,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F244),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F244)&gt;0)*ROW($F$11:F244),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J244),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-2-1</v>
       </c>
@@ -19179,8 +19179,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F245),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F245)&gt;0)*ROW($F$11:F245),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J245),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-1-1</v>
       </c>
@@ -19217,8 +19217,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F246),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F246)&gt;0)*ROW($F$11:F246),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J246),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-2-1</v>
       </c>
@@ -19251,8 +19251,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F247),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F247)&gt;0)*ROW($F$11:F247),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J247),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>86-1-1</v>
       </c>
@@ -19291,8 +19291,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F248),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F248)&gt;0)*ROW($F$11:F248),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J248),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>87-1-1</v>
       </c>
@@ -19327,8 +19327,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F249),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F249)&gt;0)*ROW($F$11:F249),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J249),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>88-1-1</v>
       </c>
@@ -19363,8 +19363,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F250),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F250)&gt;0)*ROW($F$11:F250),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J250),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>89-1-1</v>
       </c>
@@ -19399,8 +19399,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F251),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F251)&gt;0)*ROW($F$11:F251),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J251),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-1-1</v>
       </c>
@@ -19437,8 +19437,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F252),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F252)&gt;0)*ROW($F$11:F252),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J252),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-2-1</v>
       </c>
@@ -19471,8 +19471,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F253),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F253)&gt;0)*ROW($F$11:F253),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J253),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-1-1</v>
       </c>
@@ -19507,8 +19507,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F254),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F254)&gt;0)*ROW($F$11:F254),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J254),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-2-1</v>
       </c>
@@ -19541,8 +19541,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F255),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F255)&gt;0)*ROW($F$11:F255),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J255),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-3-1</v>
       </c>
@@ -19575,8 +19575,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F256),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F256)&gt;0)*ROW($F$11:F256),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J256),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-4-1</v>
       </c>
@@ -19609,8 +19609,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F257),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F257)&gt;0)*ROW($F$11:F257),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J257),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-5-1</v>
       </c>
@@ -19643,8 +19643,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F258),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F258)&gt;0)*ROW($F$11:F258),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J258),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-6-1</v>
       </c>
@@ -19677,8 +19677,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F259),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F259)&gt;0)*ROW($F$11:F259),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J259),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-7-1</v>
       </c>
@@ -19711,8 +19711,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F260),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F260)&gt;0)*ROW($F$11:F260),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J260),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-8-1</v>
       </c>
@@ -19745,8 +19745,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F261),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F261)&gt;0)*ROW($F$11:F261),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J261),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-9-1</v>
       </c>
@@ -19779,8 +19779,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F262),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F262)&gt;0)*ROW($F$11:F262),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J262),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-10-1</v>
       </c>
@@ -19813,8 +19813,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F263),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F263)&gt;0)*ROW($F$11:F263),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J263),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-11-1</v>
       </c>
@@ -19847,8 +19847,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F264),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F264)&gt;0)*ROW($F$11:F264),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J264),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-1-1</v>
       </c>
@@ -19883,8 +19883,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F265),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F265)&gt;0)*ROW($F$11:F265),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J265),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-2-1</v>
       </c>
@@ -19917,8 +19917,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F266),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F266)&gt;0)*ROW($F$11:F266),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J266),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-3-1</v>
       </c>
@@ -19951,8 +19951,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F267),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F267)&gt;0)*ROW($F$11:F267),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J267),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-4-1</v>
       </c>
@@ -19985,8 +19985,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F268),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F268)&gt;0)*ROW($F$11:F268),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J268),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-5-1</v>
       </c>
@@ -20019,8 +20019,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F269),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F269)&gt;0)*ROW($F$11:F269),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J269),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-6-1</v>
       </c>
@@ -20053,8 +20053,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F270),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F270)&gt;0)*ROW($F$11:F270),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J270),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-1-1</v>
       </c>
@@ -20089,8 +20089,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F271),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F271)&gt;0)*ROW($F$11:F271),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J271),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-2-1</v>
       </c>
@@ -20123,8 +20123,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F272),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F272)&gt;0)*ROW($F$11:F272),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J272),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-3-1</v>
       </c>
@@ -20157,8 +20157,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F273),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F273)&gt;0)*ROW($F$11:F273),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J273),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-4-1</v>
       </c>
@@ -20191,8 +20191,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F274),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F274)&gt;0)*ROW($F$11:F274),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J274),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-5-1</v>
       </c>
@@ -20225,8 +20225,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F275),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F275)&gt;0)*ROW($F$11:F275),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J275),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-6-1</v>
       </c>
@@ -20259,8 +20259,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F276),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F276)&gt;0)*ROW($F$11:F276),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J276),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-7-1</v>
       </c>
@@ -20293,8 +20293,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F277),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F277)&gt;0)*ROW($F$11:F277),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J277),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-8-1</v>
       </c>
@@ -20327,8 +20327,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F278),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F278)&gt;0)*ROW($F$11:F278),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J278),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>94-1-1</v>
       </c>
@@ -20363,8 +20363,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F279),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F279)&gt;0)*ROW($F$11:F279),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J279),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-1-1</v>
       </c>
@@ -20403,8 +20403,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F280),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F280)&gt;0)*ROW($F$11:F280),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J280),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-2-1</v>
       </c>
@@ -20435,8 +20435,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F281),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F281)&gt;0)*ROW($F$11:F281),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J281),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-3-1</v>
       </c>
@@ -20467,8 +20467,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F282),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F282)&gt;0)*ROW($F$11:F282),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J282),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-4-1</v>
       </c>
@@ -20499,8 +20499,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F283),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F283)&gt;0)*ROW($F$11:F283),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J283),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>96-1-1</v>
       </c>
@@ -20537,8 +20537,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F284),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F284)&gt;0)*ROW($F$11:F284),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J284),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>97-1-1</v>
       </c>
@@ -20571,8 +20571,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F285),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F285)&gt;0)*ROW($F$11:F285),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J285),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>98-1-1</v>
       </c>
@@ -20605,8 +20605,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F286),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F286)&gt;0)*ROW($F$11:F286),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J286),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>99-1-1</v>
       </c>
@@ -20639,8 +20639,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F287),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F287)&gt;0)*ROW($F$11:F287),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J287),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-1-1</v>
       </c>
@@ -20675,8 +20675,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F288),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F288)&gt;0)*ROW($F$11:F288),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J288),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-2-1</v>
       </c>
@@ -20707,8 +20707,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F289),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F289)&gt;0)*ROW($F$11:F289),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J289),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-3-1</v>
       </c>
@@ -20739,8 +20739,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F290),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F290)&gt;0)*ROW($F$11:F290),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J290),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-4-1</v>
       </c>
@@ -20771,8 +20771,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F291),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F291)&gt;0)*ROW($F$11:F291),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J291),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-5-1</v>
       </c>
@@ -20803,8 +20803,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F292),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F292)&gt;0)*ROW($F$11:F292),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J292),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-6-1</v>
       </c>
@@ -20835,8 +20835,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F293),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F293)&gt;0)*ROW($F$11:F293),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J293),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-7-1</v>
       </c>
@@ -20867,8 +20867,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F294),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F294)&gt;0)*ROW($F$11:F294),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J294),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-8-1</v>
       </c>
@@ -20899,8 +20899,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F295),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F295)&gt;0)*ROW($F$11:F295),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J295),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-9-1</v>
       </c>
@@ -21106,8 +21106,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F11),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F11)&gt;0)*ROW($F$11:F11),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J11),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>1-1-1</v>
       </c>
@@ -21149,8 +21149,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F12),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F12)&gt;0)*ROW($F$11:F12),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J12),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>2-1-1</v>
       </c>
@@ -21186,8 +21186,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F13),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F13)&gt;0)*ROW($F$11:F13),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J13),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-1-1</v>
       </c>
@@ -21225,8 +21225,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F14),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F14)&gt;0)*ROW($F$11:F14),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J14),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-2-1</v>
       </c>
@@ -21260,8 +21260,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F15),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F15)&gt;0)*ROW($F$11:F15),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J15),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-3-1</v>
       </c>
@@ -21295,8 +21295,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F16),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F16)&gt;0)*ROW($F$11:F16),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J16),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-4-1</v>
       </c>
@@ -21330,8 +21330,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F17),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F17)&gt;0)*ROW($F$11:F17),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J17),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-5-1</v>
       </c>
@@ -21365,8 +21365,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F18),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F18)&gt;0)*ROW($F$11:F18),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J18),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-1-1</v>
       </c>
@@ -21404,8 +21404,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F19),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F19)&gt;0)*ROW($F$11:F19),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J19),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-2-1</v>
       </c>
@@ -21439,8 +21439,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F20),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F20)&gt;0)*ROW($F$11:F20),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J20),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-3-1</v>
       </c>
@@ -21474,8 +21474,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F21),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F21)&gt;0)*ROW($F$11:F21),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J21),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-1-1</v>
       </c>
@@ -21511,8 +21511,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F22),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F22)&gt;0)*ROW($F$11:F22),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J22),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-2-1</v>
       </c>
@@ -21546,8 +21546,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F23),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F23)&gt;0)*ROW($F$11:F23),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J23),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-3-1</v>
       </c>
@@ -21581,8 +21581,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F24),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F24)&gt;0)*ROW($F$11:F24),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J24),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-4-1</v>
       </c>
@@ -21616,8 +21616,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F25),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F25)&gt;0)*ROW($F$11:F25),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J25),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-1-1</v>
       </c>
@@ -21655,8 +21655,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F26),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F26)&gt;0)*ROW($F$11:F26),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J26),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-2-1</v>
       </c>
@@ -21690,8 +21690,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F27),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F27)&gt;0)*ROW($F$11:F27),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J27),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-1-1</v>
       </c>
@@ -21729,8 +21729,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F28),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F28)&gt;0)*ROW($F$11:F28),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J28),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-2-1</v>
       </c>
@@ -21764,8 +21764,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F29),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F29)&gt;0)*ROW($F$11:F29),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J29),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-1-1</v>
       </c>
@@ -21801,8 +21801,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F30),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F30)&gt;0)*ROW($F$11:F30),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J30),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-2-1</v>
       </c>
@@ -21836,8 +21836,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F31),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F31)&gt;0)*ROW($F$11:F31),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J31),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-3-1</v>
       </c>
@@ -21871,8 +21871,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F32),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F32)&gt;0)*ROW($F$11:F32),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J32),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-4-1</v>
       </c>
@@ -21906,8 +21906,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F33),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F33)&gt;0)*ROW($F$11:F33),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J33),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-1-1</v>
       </c>
@@ -21943,8 +21943,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F34),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F34)&gt;0)*ROW($F$11:F34),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J34),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-2-1</v>
       </c>
@@ -21978,8 +21978,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F35),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F35)&gt;0)*ROW($F$11:F35),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J35),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>10-1-1</v>
       </c>
@@ -22015,8 +22015,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F36),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F36)&gt;0)*ROW($F$11:F36),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J36),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-1-1</v>
       </c>
@@ -22054,8 +22054,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F37),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F37)&gt;0)*ROW($F$11:F37),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J37),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-2-1</v>
       </c>
@@ -22087,8 +22087,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F38),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F38)&gt;0)*ROW($F$11:F38),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J38),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-3-1</v>
       </c>
@@ -22120,8 +22120,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F39),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F39)&gt;0)*ROW($F$11:F39),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J39),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-4-1</v>
       </c>
@@ -22153,8 +22153,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F40),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F40)&gt;0)*ROW($F$11:F40),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J40),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-1-1</v>
       </c>
@@ -22190,8 +22190,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F41),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F41)&gt;0)*ROW($F$11:F41),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J41),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-2-1</v>
       </c>
@@ -22223,8 +22223,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F42),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F42)&gt;0)*ROW($F$11:F42),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J42),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-1-1</v>
       </c>
@@ -22264,8 +22264,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F43),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F43)&gt;0)*ROW($F$11:F43),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J43),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-2-1</v>
       </c>
@@ -22297,8 +22297,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F44),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F44)&gt;0)*ROW($F$11:F44),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J44),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-3-1</v>
       </c>
@@ -22330,8 +22330,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F45),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F45)&gt;0)*ROW($F$11:F45),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J45),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-1-1</v>
       </c>
@@ -22365,8 +22365,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F46),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F46)&gt;0)*ROW($F$11:F46),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J46),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-2-1</v>
       </c>
@@ -22398,8 +22398,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F47),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F47)&gt;0)*ROW($F$11:F47),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J47),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-3-1</v>
       </c>
@@ -22431,8 +22431,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F48),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F48)&gt;0)*ROW($F$11:F48),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J48),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-1-1</v>
       </c>
@@ -22466,8 +22466,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F49),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F49)&gt;0)*ROW($F$11:F49),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J49),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-2-1</v>
       </c>
@@ -22499,8 +22499,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F50),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F50)&gt;0)*ROW($F$11:F50),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J50),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-1-1</v>
       </c>
@@ -22534,8 +22534,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F51),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F51)&gt;0)*ROW($F$11:F51),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J51),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-2-1</v>
       </c>
@@ -22567,8 +22567,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F52),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F52)&gt;0)*ROW($F$11:F52),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J52),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-3-1</v>
       </c>
@@ -22600,8 +22600,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F53),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F53)&gt;0)*ROW($F$11:F53),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J53),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-4-1</v>
       </c>
@@ -22633,8 +22633,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F54),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F54)&gt;0)*ROW($F$11:F54),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J54),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-5-1</v>
       </c>
@@ -22666,8 +22666,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F55),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F55)&gt;0)*ROW($F$11:F55),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J55),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-6-1</v>
       </c>
@@ -22699,8 +22699,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F56),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F56)&gt;0)*ROW($F$11:F56),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J56),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>17-1-1</v>
       </c>
@@ -22734,8 +22734,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F57),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F57)&gt;0)*ROW($F$11:F57),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J57),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>18-1-1</v>
       </c>
@@ -22769,8 +22769,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F58),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F58)&gt;0)*ROW($F$11:F58),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J58),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>19-1-1</v>
       </c>
@@ -22804,8 +22804,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F59),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F59)&gt;0)*ROW($F$11:F59),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J59),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-1-1</v>
       </c>
@@ -22841,8 +22841,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F60),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F60)&gt;0)*ROW($F$11:F60),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J60),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-2-1</v>
       </c>
@@ -22874,8 +22874,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F61),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F61)&gt;0)*ROW($F$11:F61),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J61),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-3-1</v>
       </c>
@@ -22907,8 +22907,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F62),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F62)&gt;0)*ROW($F$11:F62),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J62),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-4-1</v>
       </c>
@@ -22940,8 +22940,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F63),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F63)&gt;0)*ROW($F$11:F63),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J63),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-5-1</v>
       </c>
@@ -22973,8 +22973,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F64),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F64)&gt;0)*ROW($F$11:F64),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J64),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-1-1</v>
       </c>
@@ -23008,8 +23008,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F65),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F65)&gt;0)*ROW($F$11:F65),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J65),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-2-1</v>
       </c>
@@ -23041,8 +23041,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F66),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F66)&gt;0)*ROW($F$11:F66),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J66),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-3-1</v>
       </c>
@@ -23074,8 +23074,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F67),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F67)&gt;0)*ROW($F$11:F67),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J67),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-4-1</v>
       </c>
@@ -23107,8 +23107,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F68),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F68)&gt;0)*ROW($F$11:F68),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J68),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-5-1</v>
       </c>
@@ -23140,8 +23140,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F69),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F69)&gt;0)*ROW($F$11:F69),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J69),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-6-1</v>
       </c>
@@ -23173,8 +23173,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F70),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F70)&gt;0)*ROW($F$11:F70),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J70),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-7-1</v>
       </c>
@@ -23206,8 +23206,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F71),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F71)&gt;0)*ROW($F$11:F71),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J71),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-8-1</v>
       </c>
@@ -23239,8 +23239,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F72),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F72)&gt;0)*ROW($F$11:F72),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J72),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-1-1</v>
       </c>
@@ -23274,8 +23274,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F73),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F73)&gt;0)*ROW($F$11:F73),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J73),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-1-1</v>
       </c>
@@ -23309,8 +23309,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F74),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F74)&gt;0)*ROW($F$11:F74),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J74),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-2-1</v>
       </c>
@@ -23342,8 +23342,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F75),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F75)&gt;0)*ROW($F$11:F75),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J75),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-3-1</v>
       </c>
@@ -23375,8 +23375,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F76),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F76)&gt;0)*ROW($F$11:F76),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J76),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-4-1</v>
       </c>
@@ -23408,8 +23408,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F77),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F77)&gt;0)*ROW($F$11:F77),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J77),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-5-1</v>
       </c>
@@ -23443,8 +23443,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F78),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F78)&gt;0)*ROW($F$11:F78),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J78),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-1-1</v>
       </c>
@@ -23482,8 +23482,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F79),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F79)&gt;0)*ROW($F$11:F79),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J79),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-2-1</v>
       </c>
@@ -23515,8 +23515,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F80),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F80)&gt;0)*ROW($F$11:F80),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J80),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>25-1-1</v>
       </c>
@@ -23550,8 +23550,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F81),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F81)&gt;0)*ROW($F$11:F81),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J81),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-1-1</v>
       </c>
@@ -23585,8 +23585,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F82),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F82)&gt;0)*ROW($F$11:F82),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J82),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-2-1</v>
       </c>
@@ -23618,8 +23618,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F83),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F83)&gt;0)*ROW($F$11:F83),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J83),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>27-1-1</v>
       </c>
@@ -23653,8 +23653,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F84),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F84)&gt;0)*ROW($F$11:F84),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J84),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>28-1-1</v>
       </c>
@@ -23688,8 +23688,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F85),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F85)&gt;0)*ROW($F$11:F85),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J85),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>29-1-1</v>
       </c>
@@ -23727,8 +23727,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F86),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F86)&gt;0)*ROW($F$11:F86),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J86),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>30-1-1</v>
       </c>
@@ -23762,8 +23762,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F87),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F87)&gt;0)*ROW($F$11:F87),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J87),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>31-1-1</v>
       </c>
@@ -23797,8 +23797,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F88),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F88)&gt;0)*ROW($F$11:F88),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J88),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-1-1</v>
       </c>
@@ -23836,8 +23836,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F89),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F89)&gt;0)*ROW($F$11:F89),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J89),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-2-1</v>
       </c>
@@ -23869,8 +23869,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F90),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F90)&gt;0)*ROW($F$11:F90),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J90),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>33-1-1</v>
       </c>
@@ -23904,8 +23904,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F91),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F91)&gt;0)*ROW($F$11:F91),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J91),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-1-1</v>
       </c>
@@ -23939,8 +23939,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F92),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F92)&gt;0)*ROW($F$11:F92),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J92),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-2-1</v>
       </c>
@@ -23972,8 +23972,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F93),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F93)&gt;0)*ROW($F$11:F93),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J93),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>35-1-1</v>
       </c>
@@ -24007,8 +24007,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F94),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F94)&gt;0)*ROW($F$11:F94),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J94),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-1-1</v>
       </c>
@@ -24046,8 +24046,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F95),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F95)&gt;0)*ROW($F$11:F95),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J95),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-2-1</v>
       </c>
@@ -24079,8 +24079,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F96),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F96)&gt;0)*ROW($F$11:F96),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J96),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-3-1</v>
       </c>
@@ -24112,8 +24112,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F97),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F97)&gt;0)*ROW($F$11:F97),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J97),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-4-1</v>
       </c>
@@ -24145,8 +24145,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F98),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F98)&gt;0)*ROW($F$11:F98),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J98),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-5-1</v>
       </c>
@@ -24178,8 +24178,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F99),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F99)&gt;0)*ROW($F$11:F99),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J99),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-1-1</v>
       </c>
@@ -24213,8 +24213,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F100),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F100)&gt;0)*ROW($F$11:F100),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J100),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-2-1</v>
       </c>
@@ -24246,8 +24246,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F101),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F101)&gt;0)*ROW($F$11:F101),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J101),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-3-1</v>
       </c>
@@ -24279,8 +24279,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F102),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F102)&gt;0)*ROW($F$11:F102),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J102),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-4-1</v>
       </c>
@@ -24312,8 +24312,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F103),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F103)&gt;0)*ROW($F$11:F103),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J103),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-5-1</v>
       </c>
@@ -24345,8 +24345,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F104),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F104)&gt;0)*ROW($F$11:F104),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J104),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>38-1-1</v>
       </c>
@@ -24380,8 +24380,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F105),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F105)&gt;0)*ROW($F$11:F105),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J105),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>39-1-1</v>
       </c>
@@ -24421,8 +24421,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F106),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F106)&gt;0)*ROW($F$11:F106),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J106),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-1-1</v>
       </c>
@@ -24460,8 +24460,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F107),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F107)&gt;0)*ROW($F$11:F107),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J107),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-2-1</v>
       </c>
@@ -24493,8 +24493,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F108),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F108)&gt;0)*ROW($F$11:F108),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J108),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>41-1-1</v>
       </c>
@@ -24532,8 +24532,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F109),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F109)&gt;0)*ROW($F$11:F109),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J109),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-1-1</v>
       </c>
@@ -24571,8 +24571,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F110),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F110)&gt;0)*ROW($F$11:F110),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J110),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-2-1</v>
       </c>
@@ -24604,8 +24604,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F111),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F111)&gt;0)*ROW($F$11:F111),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J111),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-1-1</v>
       </c>
@@ -24645,8 +24645,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F112),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F112)&gt;0)*ROW($F$11:F112),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J112),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-2-1</v>
       </c>
@@ -24680,8 +24680,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F113),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F113)&gt;0)*ROW($F$11:F113),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J113),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-3-1</v>
       </c>
@@ -24713,8 +24713,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F114),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F114)&gt;0)*ROW($F$11:F114),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J114),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-4-1</v>
       </c>
@@ -24746,8 +24746,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F115),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F115)&gt;0)*ROW($F$11:F115),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J115),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-1-1</v>
       </c>
@@ -24781,8 +24781,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F116),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F116)&gt;0)*ROW($F$11:F116),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J116),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-2-1</v>
       </c>
@@ -24814,8 +24814,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F117),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F117)&gt;0)*ROW($F$11:F117),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J117),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-3-1</v>
       </c>
@@ -24847,8 +24847,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F118),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F118)&gt;0)*ROW($F$11:F118),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J118),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-4-1</v>
       </c>
@@ -24880,8 +24880,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F119),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F119)&gt;0)*ROW($F$11:F119),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J119),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-5-1</v>
       </c>
@@ -24915,8 +24915,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F120),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F120)&gt;0)*ROW($F$11:F120),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J120),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-1-1</v>
       </c>
@@ -24950,8 +24950,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F121),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F121)&gt;0)*ROW($F$11:F121),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J121),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-2-1</v>
       </c>
@@ -24983,8 +24983,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F122),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F122)&gt;0)*ROW($F$11:F122),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J122),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-3-1</v>
       </c>
@@ -25018,8 +25018,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F123),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F123)&gt;0)*ROW($F$11:F123),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J123),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-4-1</v>
       </c>
@@ -25053,8 +25053,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F124),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F124)&gt;0)*ROW($F$11:F124),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J124),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-5-1</v>
       </c>
@@ -25088,8 +25088,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F125),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F125)&gt;0)*ROW($F$11:F125),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J125),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>46-1-1</v>
       </c>
@@ -25123,8 +25123,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F126),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F126)&gt;0)*ROW($F$11:F126),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J126),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>47-1-1</v>
       </c>
@@ -25160,8 +25160,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F127),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F127)&gt;0)*ROW($F$11:F127),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J127),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>48-1-1</v>
       </c>
@@ -25201,8 +25201,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F128),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F128)&gt;0)*ROW($F$11:F128),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J128),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-1-1</v>
       </c>
@@ -25236,8 +25236,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F129),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F129)&gt;0)*ROW($F$11:F129),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J129),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-2-1</v>
       </c>
@@ -25269,8 +25269,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F130),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F130)&gt;0)*ROW($F$11:F130),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J130),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-3-1</v>
       </c>
@@ -25302,8 +25302,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F131),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F131)&gt;0)*ROW($F$11:F131),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J131),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-1-1</v>
       </c>
@@ -25343,8 +25343,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F132),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F132)&gt;0)*ROW($F$11:F132),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J132),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-2-1</v>
       </c>
@@ -25378,8 +25378,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F133),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F133)&gt;0)*ROW($F$11:F133),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J133),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-3-1</v>
       </c>
@@ -25411,8 +25411,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F134),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F134)&gt;0)*ROW($F$11:F134),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J134),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-4-1</v>
       </c>
@@ -25444,8 +25444,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F135),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F135)&gt;0)*ROW($F$11:F135),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J135),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-1-1</v>
       </c>
@@ -25479,8 +25479,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F136),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F136)&gt;0)*ROW($F$11:F136),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J136),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-2-1</v>
       </c>
@@ -25512,8 +25512,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F137),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F137)&gt;0)*ROW($F$11:F137),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J137),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>52-1-1</v>
       </c>
@@ -25549,8 +25549,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F138),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F138)&gt;0)*ROW($F$11:F138),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J138),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>53-1-1</v>
       </c>
@@ -25588,8 +25588,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F139),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F139)&gt;0)*ROW($F$11:F139),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J139),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>54-1-1</v>
       </c>
@@ -25623,8 +25623,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F140),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F140)&gt;0)*ROW($F$11:F140),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J140),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>55-1-1</v>
       </c>
@@ -25658,8 +25658,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F141),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F141)&gt;0)*ROW($F$11:F141),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J141),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>56-1-1</v>
       </c>
@@ -25695,8 +25695,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F142),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F142)&gt;0)*ROW($F$11:F142),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J142),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>57-1-1</v>
       </c>
@@ -25730,8 +25730,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F143),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F143)&gt;0)*ROW($F$11:F143),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J143),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-1-1</v>
       </c>
@@ -25767,8 +25767,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F144),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F144)&gt;0)*ROW($F$11:F144),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J144),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-2-1</v>
       </c>
@@ -25802,8 +25802,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F145),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F145)&gt;0)*ROW($F$11:F145),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J145),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-3-1</v>
       </c>
@@ -25837,8 +25837,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F146),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F146)&gt;0)*ROW($F$11:F146),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J146),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-4-1</v>
       </c>
@@ -25872,8 +25872,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F147),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F147)&gt;0)*ROW($F$11:F147),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J147),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-5-1</v>
       </c>
@@ -25907,8 +25907,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F148),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F148)&gt;0)*ROW($F$11:F148),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J148),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-6-1</v>
       </c>
@@ -25942,8 +25942,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F149),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F149)&gt;0)*ROW($F$11:F149),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J149),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-1-1</v>
       </c>
@@ -25979,8 +25979,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F150),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F150)&gt;0)*ROW($F$11:F150),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J150),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-2-1</v>
       </c>
@@ -26012,8 +26012,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F151),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F151)&gt;0)*ROW($F$11:F151),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J151),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-1-1</v>
       </c>
@@ -26047,8 +26047,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F152),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F152)&gt;0)*ROW($F$11:F152),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J152),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-2-1</v>
       </c>
@@ -26080,8 +26080,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F153),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F153)&gt;0)*ROW($F$11:F153),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J153),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-3-1</v>
       </c>
@@ -26113,8 +26113,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F154),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F154)&gt;0)*ROW($F$11:F154),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J154),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-4-1</v>
       </c>
@@ -26146,8 +26146,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F155),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F155)&gt;0)*ROW($F$11:F155),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J155),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-5-1</v>
       </c>
@@ -26179,8 +26179,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F156),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F156)&gt;0)*ROW($F$11:F156),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J156),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-6-1</v>
       </c>
@@ -26212,8 +26212,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F157),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F157)&gt;0)*ROW($F$11:F157),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J157),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-7-1</v>
       </c>
@@ -26245,8 +26245,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F158),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F158)&gt;0)*ROW($F$11:F158),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J158),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-8-1</v>
       </c>
@@ -26278,8 +26278,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F159),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F159)&gt;0)*ROW($F$11:F159),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J159),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-9-1</v>
       </c>
@@ -26311,8 +26311,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F160),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F160)&gt;0)*ROW($F$11:F160),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J160),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-10-1</v>
       </c>
@@ -26344,8 +26344,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F161),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F161)&gt;0)*ROW($F$11:F161),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J161),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-11-1</v>
       </c>
@@ -26377,8 +26377,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F162),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F162)&gt;0)*ROW($F$11:F162),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J162),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-1-1</v>
       </c>
@@ -26412,8 +26412,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F163),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F163)&gt;0)*ROW($F$11:F163),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J163),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-2-1</v>
       </c>
@@ -26445,8 +26445,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F164),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F164)&gt;0)*ROW($F$11:F164),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J164),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-3-1</v>
       </c>
@@ -26478,8 +26478,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F165),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F165)&gt;0)*ROW($F$11:F165),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J165),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-4-1</v>
       </c>
@@ -26511,8 +26511,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F166),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F166)&gt;0)*ROW($F$11:F166),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J166),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-5-1</v>
       </c>
@@ -26544,8 +26544,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F167),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F167)&gt;0)*ROW($F$11:F167),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J167),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-6-1</v>
       </c>
@@ -26579,8 +26579,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F168),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F168)&gt;0)*ROW($F$11:F168),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J168),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-7-1</v>
       </c>
@@ -26614,8 +26614,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F169),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F169)&gt;0)*ROW($F$11:F169),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J169),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-1-1</v>
       </c>
@@ -26649,8 +26649,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F170),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F170)&gt;0)*ROW($F$11:F170),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J170),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-2-1</v>
       </c>
@@ -26682,8 +26682,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F171),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F171)&gt;0)*ROW($F$11:F171),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J171),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-3-1</v>
       </c>
@@ -26715,8 +26715,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F172),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F172)&gt;0)*ROW($F$11:F172),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J172),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-4-1</v>
       </c>
@@ -26748,8 +26748,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F173),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F173)&gt;0)*ROW($F$11:F173),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J173),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-5-1</v>
       </c>
@@ -26781,8 +26781,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F174),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F174)&gt;0)*ROW($F$11:F174),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J174),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-6-1</v>
       </c>
@@ -26814,8 +26814,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F175),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F175)&gt;0)*ROW($F$11:F175),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J175),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-7-1</v>
       </c>
@@ -26849,8 +26849,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F176),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F176)&gt;0)*ROW($F$11:F176),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J176),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-8-1</v>
       </c>
@@ -26884,8 +26884,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F177),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F177)&gt;0)*ROW($F$11:F177),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J177),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-9-1</v>
       </c>
@@ -26919,8 +26919,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F178),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F178)&gt;0)*ROW($F$11:F178),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J178),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-1-1</v>
       </c>
@@ -26954,8 +26954,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F179),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F179)&gt;0)*ROW($F$11:F179),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J179),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-1-1</v>
       </c>
@@ -26991,8 +26991,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F180),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F180)&gt;0)*ROW($F$11:F180),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J180),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>65-1-1</v>
       </c>
@@ -27034,8 +27034,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F181),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F181)&gt;0)*ROW($F$11:F181),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J181),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>66-1-1</v>
       </c>
@@ -27073,8 +27073,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F182),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F182)&gt;0)*ROW($F$11:F182),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J182),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>67-1-1</v>
       </c>
@@ -27112,8 +27112,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F183),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F183)&gt;0)*ROW($F$11:F183),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J183),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>68-1-1</v>
       </c>
@@ -27155,8 +27155,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F184),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F184)&gt;0)*ROW($F$11:F184),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J184),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-1-1</v>
       </c>
@@ -27192,8 +27192,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F185),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F185)&gt;0)*ROW($F$11:F185),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J185),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-2-1</v>
       </c>
@@ -27227,8 +27227,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F186),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F186)&gt;0)*ROW($F$11:F186),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J186),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-1-1</v>
       </c>
@@ -27264,8 +27264,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F187),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F187)&gt;0)*ROW($F$11:F187),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J187),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-2-1</v>
       </c>
@@ -27299,8 +27299,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F188),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F188)&gt;0)*ROW($F$11:F188),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J188),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>71-1-1</v>
       </c>
@@ -27338,8 +27338,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F189),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F189)&gt;0)*ROW($F$11:F189),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J189),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-1-1</v>
       </c>
@@ -27379,8 +27379,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F190),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F190)&gt;0)*ROW($F$11:F190),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J190),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-2-1</v>
       </c>
@@ -27414,8 +27414,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F191),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F191)&gt;0)*ROW($F$11:F191),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J191),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-3-1</v>
       </c>
@@ -27449,8 +27449,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F192),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F192)&gt;0)*ROW($F$11:F192),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J192),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-4-1</v>
       </c>
@@ -27484,8 +27484,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F193),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F193)&gt;0)*ROW($F$11:F193),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J193),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-5-1</v>
       </c>
@@ -27519,8 +27519,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F194),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F194)&gt;0)*ROW($F$11:F194),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J194),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-6-1</v>
       </c>
@@ -27554,8 +27554,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F195),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F195)&gt;0)*ROW($F$11:F195),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J195),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-7-1</v>
       </c>
@@ -27589,8 +27589,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F196),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F196)&gt;0)*ROW($F$11:F196),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J196),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>73-1-1</v>
       </c>
@@ -27626,8 +27626,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F197),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F197)&gt;0)*ROW($F$11:F197),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J197),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-1-1</v>
       </c>
@@ -27665,8 +27665,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F198),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F198)&gt;0)*ROW($F$11:F198),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J198),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-2-1</v>
       </c>
@@ -27700,8 +27700,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F199),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F199)&gt;0)*ROW($F$11:F199),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J199),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-3-1</v>
       </c>
@@ -27735,8 +27735,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F200),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F200)&gt;0)*ROW($F$11:F200),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J200),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-4-1</v>
       </c>
@@ -27770,8 +27770,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F201),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F201)&gt;0)*ROW($F$11:F201),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J201),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-5-1</v>
       </c>
@@ -27805,8 +27805,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F202),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F202)&gt;0)*ROW($F$11:F202),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J202),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-6-1</v>
       </c>
@@ -27840,8 +27840,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F203),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F203)&gt;0)*ROW($F$11:F203),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J203),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-7-1</v>
       </c>
@@ -27875,8 +27875,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F204),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F204)&gt;0)*ROW($F$11:F204),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J204),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-8-1</v>
       </c>
@@ -27910,8 +27910,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F205),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F205)&gt;0)*ROW($F$11:F205),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J205),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-9-1</v>
       </c>
@@ -27945,8 +27945,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F206),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F206)&gt;0)*ROW($F$11:F206),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J206),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-10-1</v>
       </c>
@@ -27980,8 +27980,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F207),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F207)&gt;0)*ROW($F$11:F207),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J207),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-11-1</v>
       </c>
@@ -28015,8 +28015,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F208),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F208)&gt;0)*ROW($F$11:F208),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J208),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-12-1</v>
       </c>
@@ -28050,8 +28050,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F209),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F209)&gt;0)*ROW($F$11:F209),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J209),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-13-1</v>
       </c>
@@ -28085,8 +28085,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F210),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F210)&gt;0)*ROW($F$11:F210),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J210),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-1-1</v>
       </c>
@@ -28124,8 +28124,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F211),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F211)&gt;0)*ROW($F$11:F211),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J211),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-2-1</v>
       </c>
@@ -28159,8 +28159,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F212),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F212)&gt;0)*ROW($F$11:F212),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J212),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-3-1</v>
       </c>
@@ -28194,8 +28194,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F213),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F213)&gt;0)*ROW($F$11:F213),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J213),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-4-1</v>
       </c>
@@ -28229,8 +28229,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F214),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F214)&gt;0)*ROW($F$11:F214),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J214),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-5-1</v>
       </c>
@@ -28264,8 +28264,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F215),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F215)&gt;0)*ROW($F$11:F215),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J215),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-6-1</v>
       </c>
@@ -28299,8 +28299,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F216),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F216)&gt;0)*ROW($F$11:F216),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J216),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-7-1</v>
       </c>
@@ -28334,8 +28334,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F217),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F217)&gt;0)*ROW($F$11:F217),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J217),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-8-1</v>
       </c>
@@ -28369,8 +28369,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F218),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F218)&gt;0)*ROW($F$11:F218),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J218),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-9-1</v>
       </c>
@@ -28404,8 +28404,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F219),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F219)&gt;0)*ROW($F$11:F219),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J219),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-10-1</v>
       </c>
@@ -28439,8 +28439,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F220),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F220)&gt;0)*ROW($F$11:F220),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J220),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-11-1</v>
       </c>
@@ -28474,8 +28474,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F221),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F221)&gt;0)*ROW($F$11:F221),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J221),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-12-1</v>
       </c>
@@ -28509,8 +28509,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F222),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F222)&gt;0)*ROW($F$11:F222),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J222),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-13-1</v>
       </c>
@@ -28544,8 +28544,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F223),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F223)&gt;0)*ROW($F$11:F223),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J223),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-14-1</v>
       </c>
@@ -28579,8 +28579,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F224),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F224)&gt;0)*ROW($F$11:F224),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J224),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-15-1</v>
       </c>
@@ -28614,8 +28614,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F225),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F225)&gt;0)*ROW($F$11:F225),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J225),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-1-1</v>
       </c>
@@ -28651,8 +28651,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F226),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F226)&gt;0)*ROW($F$11:F226),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J226),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-2-1</v>
       </c>
@@ -28686,8 +28686,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F227),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F227)&gt;0)*ROW($F$11:F227),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J227),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-3-1</v>
       </c>
@@ -28721,8 +28721,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F228),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F228)&gt;0)*ROW($F$11:F228),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J228),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-1-1</v>
       </c>
@@ -28758,8 +28758,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F229),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F229)&gt;0)*ROW($F$11:F229),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J229),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>78-1-1</v>
       </c>
@@ -28795,8 +28795,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F230),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F230)&gt;0)*ROW($F$11:F230),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J230),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>79-1-1</v>
       </c>
@@ -28838,8 +28838,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F231),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F231)&gt;0)*ROW($F$11:F231),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J231),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-1-1</v>
       </c>
@@ -28875,8 +28875,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F232),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F232)&gt;0)*ROW($F$11:F232),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J232),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-2-1</v>
       </c>
@@ -28910,8 +28910,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F233),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F233)&gt;0)*ROW($F$11:F233),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J233),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-3-1</v>
       </c>
@@ -28945,8 +28945,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F234),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F234)&gt;0)*ROW($F$11:F234),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J234),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-4-1</v>
       </c>
@@ -28980,8 +28980,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F235),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F235)&gt;0)*ROW($F$11:F235),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J235),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-5-1</v>
       </c>
@@ -29015,8 +29015,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F236),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F236)&gt;0)*ROW($F$11:F236),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J236),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-1-1</v>
       </c>
@@ -29052,8 +29052,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F237),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F237)&gt;0)*ROW($F$11:F237),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J237),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-2-1</v>
       </c>
@@ -29087,8 +29087,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F238),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F238)&gt;0)*ROW($F$11:F238),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J238),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-3-1</v>
       </c>
@@ -29122,8 +29122,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F239),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F239)&gt;0)*ROW($F$11:F239),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J239),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-4-1</v>
       </c>
@@ -29157,8 +29157,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F240),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F240)&gt;0)*ROW($F$11:F240),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J240),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-5-1</v>
       </c>
@@ -29192,8 +29192,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F241),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F241)&gt;0)*ROW($F$11:F241),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J241),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>82-1-1</v>
       </c>
@@ -29229,8 +29229,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F242),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F242)&gt;0)*ROW($F$11:F242),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J242),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>83-1-1</v>
       </c>
@@ -29270,8 +29270,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F243),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F243)&gt;0)*ROW($F$11:F243),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J243),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-1-1</v>
       </c>
@@ -29313,8 +29313,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F244),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F244)&gt;0)*ROW($F$11:F244),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J244),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-2-1</v>
       </c>
@@ -29348,8 +29348,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F245),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F245)&gt;0)*ROW($F$11:F245),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J245),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-1-1</v>
       </c>
@@ -29387,8 +29387,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F246),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F246)&gt;0)*ROW($F$11:F246),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J246),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-2-1</v>
       </c>
@@ -29422,8 +29422,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F247),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F247)&gt;0)*ROW($F$11:F247),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J247),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>86-1-1</v>
       </c>
@@ -29463,8 +29463,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F248),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F248)&gt;0)*ROW($F$11:F248),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J248),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>87-1-1</v>
       </c>
@@ -29500,8 +29500,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F249),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F249)&gt;0)*ROW($F$11:F249),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J249),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>88-1-1</v>
       </c>
@@ -29537,8 +29537,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F250),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F250)&gt;0)*ROW($F$11:F250),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J250),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>89-1-1</v>
       </c>
@@ -29574,8 +29574,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F251),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F251)&gt;0)*ROW($F$11:F251),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J251),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-1-1</v>
       </c>
@@ -29613,8 +29613,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F252),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F252)&gt;0)*ROW($F$11:F252),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J252),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-2-1</v>
       </c>
@@ -29648,8 +29648,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F253),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F253)&gt;0)*ROW($F$11:F253),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J253),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-1-1</v>
       </c>
@@ -29685,8 +29685,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F254),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F254)&gt;0)*ROW($F$11:F254),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J254),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-2-1</v>
       </c>
@@ -29720,8 +29720,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F255),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F255)&gt;0)*ROW($F$11:F255),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J255),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-3-1</v>
       </c>
@@ -29755,8 +29755,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F256),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F256)&gt;0)*ROW($F$11:F256),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J256),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-4-1</v>
       </c>
@@ -29790,8 +29790,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F257),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F257)&gt;0)*ROW($F$11:F257),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J257),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-5-1</v>
       </c>
@@ -29825,8 +29825,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F258),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F258)&gt;0)*ROW($F$11:F258),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J258),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-6-1</v>
       </c>
@@ -29860,8 +29860,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F259),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F259)&gt;0)*ROW($F$11:F259),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J259),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-7-1</v>
       </c>
@@ -29895,8 +29895,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F260),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F260)&gt;0)*ROW($F$11:F260),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J260),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-8-1</v>
       </c>
@@ -29930,8 +29930,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F261),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F261)&gt;0)*ROW($F$11:F261),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J261),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-9-1</v>
       </c>
@@ -29965,8 +29965,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F262),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F262)&gt;0)*ROW($F$11:F262),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J262),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-10-1</v>
       </c>
@@ -30000,8 +30000,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F263),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F263)&gt;0)*ROW($F$11:F263),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J263),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-11-1</v>
       </c>
@@ -30035,8 +30035,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F264),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F264)&gt;0)*ROW($F$11:F264),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J264),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-1-1</v>
       </c>
@@ -30072,8 +30072,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F265),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F265)&gt;0)*ROW($F$11:F265),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J265),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-2-1</v>
       </c>
@@ -30107,8 +30107,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F266),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F266)&gt;0)*ROW($F$11:F266),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J266),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-3-1</v>
       </c>
@@ -30142,8 +30142,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F267),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F267)&gt;0)*ROW($F$11:F267),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J267),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-4-1</v>
       </c>
@@ -30177,8 +30177,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F268),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F268)&gt;0)*ROW($F$11:F268),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J268),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-5-1</v>
       </c>
@@ -30212,8 +30212,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F269),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F269)&gt;0)*ROW($F$11:F269),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J269),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-6-1</v>
       </c>
@@ -30247,8 +30247,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F270),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F270)&gt;0)*ROW($F$11:F270),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J270),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-1-1</v>
       </c>
@@ -30284,8 +30284,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F271),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F271)&gt;0)*ROW($F$11:F271),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J271),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-2-1</v>
       </c>
@@ -30319,8 +30319,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F272),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F272)&gt;0)*ROW($F$11:F272),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J272),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-3-1</v>
       </c>
@@ -30354,8 +30354,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F273),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F273)&gt;0)*ROW($F$11:F273),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J273),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-4-1</v>
       </c>
@@ -30389,8 +30389,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F274),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F274)&gt;0)*ROW($F$11:F274),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J274),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-5-1</v>
       </c>
@@ -30424,8 +30424,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F275),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F275)&gt;0)*ROW($F$11:F275),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J275),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-6-1</v>
       </c>
@@ -30459,8 +30459,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F276),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F276)&gt;0)*ROW($F$11:F276),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J276),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-7-1</v>
       </c>
@@ -30494,8 +30494,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F277),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F277)&gt;0)*ROW($F$11:F277),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J277),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-8-1</v>
       </c>
@@ -30529,8 +30529,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F278),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F278)&gt;0)*ROW($F$11:F278),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J278),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>94-1-1</v>
       </c>
@@ -30566,8 +30566,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F279),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F279)&gt;0)*ROW($F$11:F279),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J279),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-1-1</v>
       </c>
@@ -30607,8 +30607,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F280),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F280)&gt;0)*ROW($F$11:F280),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J280),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-2-1</v>
       </c>
@@ -30640,8 +30640,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F281),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F281)&gt;0)*ROW($F$11:F281),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J281),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-3-1</v>
       </c>
@@ -30673,8 +30673,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F282),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F282)&gt;0)*ROW($F$11:F282),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J282),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-4-1</v>
       </c>
@@ -30706,8 +30706,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F283),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F283)&gt;0)*ROW($F$11:F283),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J283),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>96-1-1</v>
       </c>
@@ -30745,8 +30745,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F284),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F284)&gt;0)*ROW($F$11:F284),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J284),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>97-1-1</v>
       </c>
@@ -30780,8 +30780,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F285),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F285)&gt;0)*ROW($F$11:F285),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J285),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>98-1-1</v>
       </c>
@@ -30815,8 +30815,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F286),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F286)&gt;0)*ROW($F$11:F286),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J286),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>99-1-1</v>
       </c>
@@ -30850,8 +30850,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F287),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F287)&gt;0)*ROW($F$11:F287),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J287),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-1-1</v>
       </c>
@@ -30887,8 +30887,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F288),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F288)&gt;0)*ROW($F$11:F288),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J288),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-2-1</v>
       </c>
@@ -30920,8 +30920,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F289),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F289)&gt;0)*ROW($F$11:F289),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J289),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-3-1</v>
       </c>
@@ -30953,8 +30953,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F290),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F290)&gt;0)*ROW($F$11:F290),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J290),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-4-1</v>
       </c>
@@ -30986,8 +30986,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F291),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F291)&gt;0)*ROW($F$11:F291),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J291),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-5-1</v>
       </c>
@@ -31019,8 +31019,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F292),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F292)&gt;0)*ROW($F$11:F292),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J292),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-6-1</v>
       </c>
@@ -31052,8 +31052,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F293),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F293)&gt;0)*ROW($F$11:F293),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J293),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-7-1</v>
       </c>
@@ -31085,8 +31085,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F294),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F294)&gt;0)*ROW($F$11:F294),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J294),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-8-1</v>
       </c>
@@ -31118,8 +31118,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F295),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F295)&gt;0)*ROW($F$11:F295),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J295),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-9-1</v>
       </c>
@@ -31151,8 +31151,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F296),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F296)&gt;0)*ROW($F$11:F296),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J296),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-1-1</v>
       </c>
@@ -31192,8 +31192,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F297),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F297)&gt;0)*ROW($F$11:F297),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J297),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-2-1</v>
       </c>
@@ -31225,8 +31225,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F298),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F298)&gt;0)*ROW($F$11:F298),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J298),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-3-1</v>
       </c>
@@ -31258,8 +31258,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F299),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F299)&gt;0)*ROW($F$11:F299),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J299),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-4-1</v>
       </c>
@@ -31291,8 +31291,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F300),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F300)&gt;0)*ROW($F$11:F300),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J300),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>102-1-1</v>
       </c>
@@ -31326,8 +31326,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F301),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F301)&gt;0)*ROW($F$11:F301),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J301),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>103-1-1</v>
       </c>
@@ -31361,8 +31361,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F302),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F302)&gt;0)*ROW($F$11:F302),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J302),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>104-1-1</v>
       </c>
@@ -31398,8 +31398,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F303),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F303)&gt;0)*ROW($F$11:F303),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J303),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-1-1</v>
       </c>
@@ -31435,8 +31435,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F304),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F304)&gt;0)*ROW($F$11:F304),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J304),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>106-1-1</v>
       </c>
@@ -31472,8 +31472,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F305),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F305)&gt;0)*ROW($F$11:F305),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J305),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>106-2-1</v>
       </c>
@@ -31505,8 +31505,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F306),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F306)&gt;0)*ROW($F$11:F306),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J306),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>106-3-1</v>
       </c>
@@ -31538,8 +31538,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F307),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F307)&gt;0)*ROW($F$11:F307),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J307),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>107-1-1</v>
       </c>
@@ -31575,8 +31575,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F308),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F308)&gt;0)*ROW($F$11:F308),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J308),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>107-2-1</v>
       </c>
@@ -31608,8 +31608,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F309),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F309)&gt;0)*ROW($F$11:F309),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J309),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>107-3-1</v>
       </c>
@@ -31641,8 +31641,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F310),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F310)&gt;0)*ROW($F$11:F310),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J310),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-1-1</v>
       </c>
@@ -31678,8 +31678,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F311),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F311)&gt;0)*ROW($F$11:F311),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J311),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-2-1</v>
       </c>
@@ -31711,8 +31711,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F312),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F312)&gt;0)*ROW($F$11:F312),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J312),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-3-1</v>
       </c>
@@ -31744,8 +31744,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F313),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F313)&gt;0)*ROW($F$11:F313),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J313),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-4-1</v>
       </c>
@@ -31777,8 +31777,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F314),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F314)&gt;0)*ROW($F$11:F314),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J314),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-5-1</v>
       </c>
@@ -31810,8 +31810,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F315),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F315)&gt;0)*ROW($F$11:F315),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J315),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-6-1</v>
       </c>
@@ -31843,8 +31843,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F316),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F316)&gt;0)*ROW($F$11:F316),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J316),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-7-1</v>
       </c>
@@ -31876,8 +31876,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F317),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F317)&gt;0)*ROW($F$11:F317),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J317),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-8-1</v>
       </c>
@@ -31909,8 +31909,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F318),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F318)&gt;0)*ROW($F$11:F318),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J318),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>109-1-1</v>
       </c>
@@ -31950,8 +31950,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F319),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F319)&gt;0)*ROW($F$11:F319),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J319),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>110-1-1</v>
       </c>
@@ -32151,11 +32151,11 @@
 _xlpm.確認観点1数, COUNTA($C$11:C11),
 _xlpm.直近で確認観点1が空でないセルの行番号, MAX(INDEX((LEN($C$11:C11)&gt;0)*ROW($C$11:C11),0)),
 _xlpm.確認観点2数, COUNTA(INDIRECT("D"&amp;_xlpm.直近で確認観点1が空でないセルの行番号):D11),
-_xlpm.確認観点2数（確認観点2が空の場合は1）,IF(_xlpm.確認観点2数=0,1,_xlpm.確認観点2数),
+_xlpm.確認観点2数_空なら1,IF(_xlpm.確認観点2数=0,1,_xlpm.確認観点2数),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D11)&gt;0)*ROW($D$11:D11),0),_xlpm.直近で確認観点1が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("H"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):H11),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点1が空でないセルの行番号&gt;_xlpm.直近で確認観点2が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点1数&amp;"-"&amp;_xlpm.確認観点2数（確認観点2が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点1が空でないセルの行番号&gt;_xlpm.直近で確認観点2が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点1数&amp;"-"&amp;_xlpm.確認観点2数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>1-1-1</v>
       </c>
@@ -32187,11 +32187,11 @@
 _xlpm.確認観点1数, COUNTA($C$11:C12),
 _xlpm.直近で確認観点1が空でないセルの行番号, MAX(INDEX((LEN($C$11:C12)&gt;0)*ROW($C$11:C12),0)),
 _xlpm.確認観点2数, COUNTA(INDIRECT("D"&amp;_xlpm.直近で確認観点1が空でないセルの行番号):D12),
-_xlpm.確認観点2数（確認観点2が空の場合は1）,IF(_xlpm.確認観点2数=0,1,_xlpm.確認観点2数),
+_xlpm.確認観点2数_空なら1,IF(_xlpm.確認観点2数=0,1,_xlpm.確認観点2数),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D12)&gt;0)*ROW($D$11:D12),0),_xlpm.直近で確認観点1が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("H"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):H12),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点1が空でないセルの行番号&gt;_xlpm.直近で確認観点2が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点1数&amp;"-"&amp;_xlpm.確認観点2数（確認観点2が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点1が空でないセルの行番号&gt;_xlpm.直近で確認観点2が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点1数&amp;"-"&amp;_xlpm.確認観点2数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>1-2-1</v>
       </c>
@@ -32219,11 +32219,11 @@
 _xlpm.確認観点1数, COUNTA($C$11:C13),
 _xlpm.直近で確認観点1が空でないセルの行番号, MAX(INDEX((LEN($C$11:C13)&gt;0)*ROW($C$11:C13),0)),
 _xlpm.確認観点2数, COUNTA(INDIRECT("D"&amp;_xlpm.直近で確認観点1が空でないセルの行番号):D13),
-_xlpm.確認観点2数（確認観点2が空の場合は1）,IF(_xlpm.確認観点2数=0,1,_xlpm.確認観点2数),
+_xlpm.確認観点2数_空なら1,IF(_xlpm.確認観点2数=0,1,_xlpm.確認観点2数),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D13)&gt;0)*ROW($D$11:D13),0),_xlpm.直近で確認観点1が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("H"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):H13),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点1が空でないセルの行番号&gt;_xlpm.直近で確認観点2が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点1数&amp;"-"&amp;_xlpm.確認観点2数（確認観点2が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点1が空でないセルの行番号&gt;_xlpm.直近で確認観点2が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点1数&amp;"-"&amp;_xlpm.確認観点2数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>2-1-1</v>
       </c>
@@ -32252,11 +32252,11 @@
 _xlpm.確認観点1数, COUNTA($C$11:C14),
 _xlpm.直近で確認観点1が空でないセルの行番号, MAX(INDEX((LEN($C$11:C14)&gt;0)*ROW($C$11:C14),0)),
 _xlpm.確認観点2数, COUNTA(INDIRECT("D"&amp;_xlpm.直近で確認観点1が空でないセルの行番号):D14),
-_xlpm.確認観点2数（確認観点2が空の場合は1）,IF(_xlpm.確認観点2数=0,1,_xlpm.確認観点2数),
+_xlpm.確認観点2数_空なら1,IF(_xlpm.確認観点2数=0,1,_xlpm.確認観点2数),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D14)&gt;0)*ROW($D$11:D14),0),_xlpm.直近で確認観点1が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("H"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):H14),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点1が空でないセルの行番号&gt;_xlpm.直近で確認観点2が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点1数&amp;"-"&amp;_xlpm.確認観点2数（確認観点2が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点1が空でないセルの行番号&gt;_xlpm.直近で確認観点2が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点1数&amp;"-"&amp;_xlpm.確認観点2数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>2-2-1</v>
       </c>
